--- a/models/pairwise_wald_tests.xlsx
+++ b/models/pairwise_wald_tests.xlsx
@@ -1,473 +1,480 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xnw17/Documents/GitHub/Conjoint_Survey_25/models/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE18D137-E0EF-5046-9E74-B79E7049F17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="26160" windowHeight="14440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Budget" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Adoption" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Budget" sheetId="1" r:id="rId1"/>
+    <sheet name="Adoption" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
-  <si>
-    <t xml:space="preserve">Parameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_low vs. car_high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_low vs. suv_low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_low vs. suv_high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_high vs. suv_low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_high vs. suv_high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">suv_low vs. suv_high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">λ (scale)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.160***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.754***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.808***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.212***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.734***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEV powertrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.806**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.798***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.737***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEV powertrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.513***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.311***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.361***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.171**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electric range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.378*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.198*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mileage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.519***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.011**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.920***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.404***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.860.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.276***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.039***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.824.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.082***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.773***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.353***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.366***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.735**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.359***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.708***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.192**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.703***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.650***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.754***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.801***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.736.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.950***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full results (long form):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">group1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">group2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z_stat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scalePar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">powertrainbev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">powertrainhev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_bev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mileage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">operating_cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no_choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">suv_low</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">suv_high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_likely vs. car_unlikely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_likely vs. suv_likely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_likely vs. suv_unlikely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_unlikely vs. suv_likely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_unlikely vs. suv_unlikely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">suv_likely vs. suv_unlikely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.501***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.183**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.674***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.577***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.553***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.787***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.735.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.537***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.001***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.813**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.418***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.840***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.878***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.137***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.293***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.351*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.697.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.530*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.830**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.141***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.467***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.648.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.625***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.253*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.065***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.049***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.889**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.163**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.072**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.914.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.095***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.907***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.018***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.444***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.953**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_likely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">car_unlikely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">suv_likely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">suv_unlikely</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="149">
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>car_low vs. car_high</t>
+  </si>
+  <si>
+    <t>car_low vs. suv_low</t>
+  </si>
+  <si>
+    <t>car_low vs. suv_high</t>
+  </si>
+  <si>
+    <t>car_high vs. suv_low</t>
+  </si>
+  <si>
+    <t>car_high vs. suv_high</t>
+  </si>
+  <si>
+    <t>suv_low vs. suv_high</t>
+  </si>
+  <si>
+    <t>λ (scale)</t>
+  </si>
+  <si>
+    <t>16.160***</t>
+  </si>
+  <si>
+    <t>6.754***</t>
+  </si>
+  <si>
+    <t>16.808***</t>
+  </si>
+  <si>
+    <t>-9.212***</t>
+  </si>
+  <si>
+    <t>0.169</t>
+  </si>
+  <si>
+    <t>9.734***</t>
+  </si>
+  <si>
+    <t>BEV powertrain</t>
+  </si>
+  <si>
+    <t>2.806**</t>
+  </si>
+  <si>
+    <t>4.798***</t>
+  </si>
+  <si>
+    <t>3.737***</t>
+  </si>
+  <si>
+    <t>0.716</t>
+  </si>
+  <si>
+    <t>0.926</t>
+  </si>
+  <si>
+    <t>0.373</t>
+  </si>
+  <si>
+    <t>HEV powertrain</t>
+  </si>
+  <si>
+    <t>-4.513***</t>
+  </si>
+  <si>
+    <t>0.229</t>
+  </si>
+  <si>
+    <t>-3.311***</t>
+  </si>
+  <si>
+    <t>4.361***</t>
+  </si>
+  <si>
+    <t>1.456</t>
+  </si>
+  <si>
+    <t>-3.171**</t>
+  </si>
+  <si>
+    <t>Electric range</t>
+  </si>
+  <si>
+    <t>-2.378*</t>
+  </si>
+  <si>
+    <t>-2.198*</t>
+  </si>
+  <si>
+    <t>-1.308</t>
+  </si>
+  <si>
+    <t>0.731</t>
+  </si>
+  <si>
+    <t>1.116</t>
+  </si>
+  <si>
+    <t>0.545</t>
+  </si>
+  <si>
+    <t>Mileage</t>
+  </si>
+  <si>
+    <t>7.519***</t>
+  </si>
+  <si>
+    <t>3.011**</t>
+  </si>
+  <si>
+    <t>10.920***</t>
+  </si>
+  <si>
+    <t>-5.404***</t>
+  </si>
+  <si>
+    <t>1.860.</t>
+  </si>
+  <si>
+    <t>8.276***</t>
+  </si>
+  <si>
+    <t>Vehicle age</t>
+  </si>
+  <si>
+    <t>9.039***</t>
+  </si>
+  <si>
+    <t>1.824.</t>
+  </si>
+  <si>
+    <t>12.082***</t>
+  </si>
+  <si>
+    <t>-7.773***</t>
+  </si>
+  <si>
+    <t>1.056</t>
+  </si>
+  <si>
+    <t>10.353***</t>
+  </si>
+  <si>
+    <t>Operating cost</t>
+  </si>
+  <si>
+    <t>5.366***</t>
+  </si>
+  <si>
+    <t>2.735**</t>
+  </si>
+  <si>
+    <t>5.359***</t>
+  </si>
+  <si>
+    <t>-3.708***</t>
+  </si>
+  <si>
+    <t>-1.012</t>
+  </si>
+  <si>
+    <t>3.192**</t>
+  </si>
+  <si>
+    <t>No choice</t>
+  </si>
+  <si>
+    <t>13.703***</t>
+  </si>
+  <si>
+    <t>7.650***</t>
+  </si>
+  <si>
+    <t>19.754***</t>
+  </si>
+  <si>
+    <t>-8.801***</t>
+  </si>
+  <si>
+    <t>1.736.</t>
+  </si>
+  <si>
+    <t>12.950***</t>
+  </si>
+  <si>
+    <t>Full results (long form):</t>
+  </si>
+  <si>
+    <t>group1</t>
+  </si>
+  <si>
+    <t>group2</t>
+  </si>
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>b1</t>
+  </si>
+  <si>
+    <t>se1</t>
+  </si>
+  <si>
+    <t>b2</t>
+  </si>
+  <si>
+    <t>se2</t>
+  </si>
+  <si>
+    <t>z_stat</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>sig</t>
+  </si>
+  <si>
+    <t>car_low</t>
+  </si>
+  <si>
+    <t>car_high</t>
+  </si>
+  <si>
+    <t>scalePar</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>powertrainbev</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>powertrainhev</t>
+  </si>
+  <si>
+    <t>range_bev</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>mileage</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>operating_cost</t>
+  </si>
+  <si>
+    <t>no_choice</t>
+  </si>
+  <si>
+    <t>suv_low</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>suv_high</t>
+  </si>
+  <si>
+    <t>car_likely vs. car_unlikely</t>
+  </si>
+  <si>
+    <t>car_likely vs. suv_likely</t>
+  </si>
+  <si>
+    <t>car_likely vs. suv_unlikely</t>
+  </si>
+  <si>
+    <t>car_unlikely vs. suv_likely</t>
+  </si>
+  <si>
+    <t>car_unlikely vs. suv_unlikely</t>
+  </si>
+  <si>
+    <t>suv_likely vs. suv_unlikely</t>
+  </si>
+  <si>
+    <t>-3.501***</t>
+  </si>
+  <si>
+    <t>3.183**</t>
+  </si>
+  <si>
+    <t>-0.119</t>
+  </si>
+  <si>
+    <t>6.674***</t>
+  </si>
+  <si>
+    <t>3.577***</t>
+  </si>
+  <si>
+    <t>-3.553***</t>
+  </si>
+  <si>
+    <t>7.787***</t>
+  </si>
+  <si>
+    <t>1.735.</t>
+  </si>
+  <si>
+    <t>7.537***</t>
+  </si>
+  <si>
+    <t>-4.001***</t>
+  </si>
+  <si>
+    <t>2.813**</t>
+  </si>
+  <si>
+    <t>5.418***</t>
+  </si>
+  <si>
+    <t>7.840***</t>
+  </si>
+  <si>
+    <t>-0.246</t>
+  </si>
+  <si>
+    <t>7.878***</t>
+  </si>
+  <si>
+    <t>-7.137***</t>
+  </si>
+  <si>
+    <t>0.798</t>
+  </si>
+  <si>
+    <t>7.293***</t>
+  </si>
+  <si>
+    <t>2.351*</t>
+  </si>
+  <si>
+    <t>0.617</t>
+  </si>
+  <si>
+    <t>0.791</t>
+  </si>
+  <si>
+    <t>-1.697.</t>
+  </si>
+  <si>
+    <t>-1.078</t>
+  </si>
+  <si>
+    <t>0.313</t>
+  </si>
+  <si>
+    <t>-2.530*</t>
+  </si>
+  <si>
+    <t>2.830**</t>
+  </si>
+  <si>
+    <t>1.516</t>
+  </si>
+  <si>
+    <t>5.141***</t>
+  </si>
+  <si>
+    <t>4.467***</t>
+  </si>
+  <si>
+    <t>-1.648.</t>
+  </si>
+  <si>
+    <t>-1.446</t>
+  </si>
+  <si>
+    <t>4.625***</t>
+  </si>
+  <si>
+    <t>2.253*</t>
+  </si>
+  <si>
+    <t>6.065***</t>
+  </si>
+  <si>
+    <t>4.049***</t>
+  </si>
+  <si>
+    <t>-2.889**</t>
+  </si>
+  <si>
+    <t>-3.163**</t>
+  </si>
+  <si>
+    <t>0.291</t>
+  </si>
+  <si>
+    <t>-1.420</t>
+  </si>
+  <si>
+    <t>3.072**</t>
+  </si>
+  <si>
+    <t>1.914.</t>
+  </si>
+  <si>
+    <t>-1.565</t>
+  </si>
+  <si>
+    <t>-4.095***</t>
+  </si>
+  <si>
+    <t>3.907***</t>
+  </si>
+  <si>
+    <t>1.636</t>
+  </si>
+  <si>
+    <t>8.018***</t>
+  </si>
+  <si>
+    <t>7.444***</t>
+  </si>
+  <si>
+    <t>-2.953**</t>
+  </si>
+  <si>
+    <t>car_likely</t>
+  </si>
+  <si>
+    <t>car_unlikely</t>
+  </si>
+  <si>
+    <t>suv_likely</t>
+  </si>
+  <si>
+    <t>suv_unlikely</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -496,13 +503,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -784,11 +803,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -811,7 +833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -834,7 +856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -857,7 +879,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -880,7 +902,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -903,7 +925,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -926,7 +948,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -949,7 +971,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -972,7 +994,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -995,12 +1017,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -1032,7 +1054,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -1042,29 +1064,29 @@
       <c r="C14" t="s">
         <v>76</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>3.66</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="E14">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="F14">
+        <v>1.2230000000000001</v>
+      </c>
+      <c r="G14">
+        <v>6.3E-2</v>
+      </c>
+      <c r="H14">
         <v>16.16</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -1074,29 +1096,29 @@
       <c r="C15" t="s">
         <v>78</v>
       </c>
-      <c r="D15" t="n">
-        <v>-1.019</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.807</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="D15">
+        <v>-1.0189999999999999</v>
+      </c>
+      <c r="E15">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="F15">
+        <v>-1.8069999999999999</v>
+      </c>
+      <c r="G15">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="H15">
         <v>2.806</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.005</v>
+      <c r="I15">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="J15" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -1106,29 +1128,29 @@
       <c r="C16" t="s">
         <v>80</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>-0.06</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-4.513</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="E16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F16">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="G16">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H16">
+        <v>-4.5129999999999999</v>
+      </c>
+      <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -1138,29 +1160,29 @@
       <c r="C17" t="s">
         <v>81</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="D17">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="E17">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="F17">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="G17">
         <v>0.121</v>
       </c>
-      <c r="H17" t="n">
-        <v>-2.378</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.0174</v>
+      <c r="H17">
+        <v>-2.3780000000000001</v>
+      </c>
+      <c r="I17">
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="J17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -1170,29 +1192,29 @@
       <c r="C18" t="s">
         <v>83</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>-0.1</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="E18">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F18">
         <v>-0.315</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="H18" t="n">
-        <v>7.519</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="G18">
+        <v>2.7E-2</v>
+      </c>
+      <c r="H18">
+        <v>7.5190000000000001</v>
+      </c>
+      <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1202,29 +1224,29 @@
       <c r="C19" t="s">
         <v>84</v>
       </c>
-      <c r="D19" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="D19">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="E19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F19">
         <v>-0.191</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="H19" t="n">
-        <v>9.039</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="G19">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="H19">
+        <v>9.0389999999999997</v>
+      </c>
+      <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -1234,29 +1256,29 @@
       <c r="C20" t="s">
         <v>85</v>
       </c>
-      <c r="D20" t="n">
-        <v>-0.413</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-1.047</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="D20">
+        <v>-0.41299999999999998</v>
+      </c>
+      <c r="E20">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F20">
+        <v>-1.0469999999999999</v>
+      </c>
+      <c r="G20">
         <v>0.114</v>
       </c>
-      <c r="H20" t="n">
-        <v>5.366</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="H20">
+        <v>5.3659999999999997</v>
+      </c>
+      <c r="I20">
         <v>0</v>
       </c>
       <c r="J20" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>74</v>
       </c>
@@ -1266,29 +1288,29 @@
       <c r="C21" t="s">
         <v>86</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>-3.327</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.086</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-7.761</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="E21">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="F21">
+        <v>-7.7610000000000001</v>
+      </c>
+      <c r="G21">
         <v>0.312</v>
       </c>
-      <c r="H21" t="n">
-        <v>13.703</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H21">
+        <v>13.702999999999999</v>
+      </c>
+      <c r="I21">
         <v>0</v>
       </c>
       <c r="J21" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -1298,29 +1320,29 @@
       <c r="C22" t="s">
         <v>76</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>3.66</v>
       </c>
-      <c r="E22" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6.754</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="E22">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="F22">
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="G22">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="H22">
+        <v>6.7539999999999996</v>
+      </c>
+      <c r="I22">
         <v>0</v>
       </c>
       <c r="J22" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -1330,29 +1352,29 @@
       <c r="C23" t="s">
         <v>78</v>
       </c>
-      <c r="D23" t="n">
-        <v>-1.019</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-2.046</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="D23">
+        <v>-1.0189999999999999</v>
+      </c>
+      <c r="E23">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="F23">
+        <v>-2.0459999999999998</v>
+      </c>
+      <c r="G23">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="H23">
         <v>4.798</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>0</v>
       </c>
       <c r="J23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -1362,29 +1384,29 @@
       <c r="C24" t="s">
         <v>80</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>-0.06</v>
       </c>
-      <c r="E24" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0.073</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="E24">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F24">
+        <v>-7.2999999999999995E-2</v>
+      </c>
+      <c r="G24">
         <v>0.05</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.8186</v>
+      <c r="H24">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="I24">
+        <v>0.81859999999999999</v>
       </c>
       <c r="J24" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -1394,29 +1416,29 @@
       <c r="C25" t="s">
         <v>81</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="D25">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="E25">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="F25">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="G25">
+        <v>7.8E-2</v>
+      </c>
+      <c r="H25">
         <v>-2.198</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.0279</v>
+      <c r="I25">
+        <v>2.7900000000000001E-2</v>
       </c>
       <c r="J25" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1426,29 +1448,29 @@
       <c r="C26" t="s">
         <v>83</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>-0.1</v>
       </c>
-      <c r="E26" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.148</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3.011</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0026</v>
+      <c r="E26">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F26">
+        <v>-0.14799999999999999</v>
+      </c>
+      <c r="G26">
+        <v>1.4E-2</v>
+      </c>
+      <c r="H26">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="I26">
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="J26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -1458,29 +1480,29 @@
       <c r="C27" t="s">
         <v>84</v>
       </c>
-      <c r="D27" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0.043</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.824</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.0681</v>
+      <c r="D27">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="E27">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F27">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+      <c r="G27">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="H27">
+        <v>1.8240000000000001</v>
+      </c>
+      <c r="I27">
+        <v>6.8099999999999994E-2</v>
       </c>
       <c r="J27" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -1490,29 +1512,29 @@
       <c r="C28" t="s">
         <v>85</v>
       </c>
-      <c r="D28" t="n">
-        <v>-0.413</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-0.583</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.0062</v>
+      <c r="D28">
+        <v>-0.41299999999999998</v>
+      </c>
+      <c r="E28">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F28">
+        <v>-0.58299999999999996</v>
+      </c>
+      <c r="G28">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="H28">
+        <v>2.7349999999999999</v>
+      </c>
+      <c r="I28">
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="J28" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -1522,29 +1544,29 @@
       <c r="C29" t="s">
         <v>86</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>-3.327</v>
       </c>
-      <c r="E29" t="n">
-        <v>0.086</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-4.691</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="E29">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="F29">
+        <v>-4.6909999999999998</v>
+      </c>
+      <c r="G29">
         <v>0.156</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>7.65</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>0</v>
       </c>
       <c r="J29" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -1554,29 +1576,29 @@
       <c r="C30" t="s">
         <v>76</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>3.66</v>
       </c>
-      <c r="E30" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.209</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="E30">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="F30">
+        <v>1.2090000000000001</v>
+      </c>
+      <c r="G30">
         <v>0.05</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>16.808</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>0</v>
       </c>
       <c r="J30" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1586,29 +1608,29 @@
       <c r="C31" t="s">
         <v>78</v>
       </c>
-      <c r="D31" t="n">
-        <v>-1.019</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="D31">
+        <v>-1.0189999999999999</v>
+      </c>
+      <c r="E31">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="F31">
+        <v>-2.1800000000000002</v>
+      </c>
+      <c r="G31">
         <v>0.3</v>
       </c>
-      <c r="H31" t="n">
-        <v>3.737</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.0002</v>
+      <c r="H31">
+        <v>3.7370000000000001</v>
+      </c>
+      <c r="I31">
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="J31" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1618,29 +1640,29 @@
       <c r="C32" t="s">
         <v>80</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>-0.06</v>
       </c>
-      <c r="E32" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-3.311</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.0009</v>
+      <c r="E32">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F32">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="G32">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H32">
+        <v>-3.3109999999999999</v>
+      </c>
+      <c r="I32">
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="J32" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1650,29 +1672,29 @@
       <c r="C33" t="s">
         <v>81</v>
       </c>
-      <c r="D33" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-1.308</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.1907</v>
+      <c r="D33">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="E33">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="F33">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="G33">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H33">
+        <v>-1.3080000000000001</v>
+      </c>
+      <c r="I33">
+        <v>0.19070000000000001</v>
       </c>
       <c r="J33" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -1682,29 +1704,29 @@
       <c r="C34" t="s">
         <v>83</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>-0.1</v>
       </c>
-      <c r="E34" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.384</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="E34">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F34">
+        <v>-0.38400000000000001</v>
+      </c>
+      <c r="G34">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H34">
         <v>10.92</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>0</v>
       </c>
       <c r="J34" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -1714,29 +1736,29 @@
       <c r="C35" t="s">
         <v>84</v>
       </c>
-      <c r="D35" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="D35">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="E35">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F35">
         <v>-0.216</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H35" t="n">
-        <v>12.082</v>
-      </c>
-      <c r="I35" t="n">
+      <c r="G35">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H35">
+        <v>12.082000000000001</v>
+      </c>
+      <c r="I35">
         <v>0</v>
       </c>
       <c r="J35" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1746,29 +1768,29 @@
       <c r="C36" t="s">
         <v>85</v>
       </c>
-      <c r="D36" t="n">
-        <v>-0.413</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.903</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="D36">
+        <v>-0.41299999999999998</v>
+      </c>
+      <c r="E36">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F36">
+        <v>-0.90300000000000002</v>
+      </c>
+      <c r="G36">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H36">
         <v>5.359</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>0</v>
       </c>
       <c r="J36" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -1778,29 +1800,29 @@
       <c r="C37" t="s">
         <v>86</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>-3.327</v>
       </c>
-      <c r="E37" t="n">
-        <v>0.086</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-8.449</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="E37">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="F37">
+        <v>-8.4489999999999998</v>
+      </c>
+      <c r="G37">
         <v>0.245</v>
       </c>
-      <c r="H37" t="n">
-        <v>19.754</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="H37">
+        <v>19.754000000000001</v>
+      </c>
+      <c r="I37">
         <v>0</v>
       </c>
       <c r="J37" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -1810,29 +1832,29 @@
       <c r="C38" t="s">
         <v>76</v>
       </c>
-      <c r="D38" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="F38" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-9.212</v>
-      </c>
-      <c r="I38" t="n">
+      <c r="D38">
+        <v>1.2230000000000001</v>
+      </c>
+      <c r="E38">
+        <v>6.3E-2</v>
+      </c>
+      <c r="F38">
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="G38">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="H38">
+        <v>-9.2119999999999997</v>
+      </c>
+      <c r="I38">
         <v>0</v>
       </c>
       <c r="J38" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>75</v>
       </c>
@@ -1842,29 +1864,29 @@
       <c r="C39" t="s">
         <v>78</v>
       </c>
-      <c r="D39" t="n">
-        <v>-1.807</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-2.046</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="I39" t="n">
+      <c r="D39">
+        <v>-1.8069999999999999</v>
+      </c>
+      <c r="E39">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="F39">
+        <v>-2.0459999999999998</v>
+      </c>
+      <c r="G39">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="H39">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="I39">
         <v>0.4738</v>
       </c>
       <c r="J39" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -1874,29 +1896,29 @@
       <c r="C40" t="s">
         <v>80</v>
       </c>
-      <c r="D40" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-0.073</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="D40">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="E40">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="F40">
+        <v>-7.2999999999999995E-2</v>
+      </c>
+      <c r="G40">
         <v>0.05</v>
       </c>
-      <c r="H40" t="n">
-        <v>4.361</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="H40">
+        <v>4.3609999999999998</v>
+      </c>
+      <c r="I40">
         <v>0</v>
       </c>
       <c r="J40" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>75</v>
       </c>
@@ -1906,29 +1928,29 @@
       <c r="C41" t="s">
         <v>81</v>
       </c>
-      <c r="D41" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="D41">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="E41">
         <v>0.121</v>
       </c>
-      <c r="F41" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.4651</v>
+      <c r="F41">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="G41">
+        <v>7.8E-2</v>
+      </c>
+      <c r="H41">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="I41">
+        <v>0.46510000000000001</v>
       </c>
       <c r="J41" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>75</v>
       </c>
@@ -1938,29 +1960,29 @@
       <c r="C42" t="s">
         <v>83</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>-0.315</v>
       </c>
-      <c r="E42" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-0.148</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-5.404</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="E42">
+        <v>2.7E-2</v>
+      </c>
+      <c r="F42">
+        <v>-0.14799999999999999</v>
+      </c>
+      <c r="G42">
+        <v>1.4E-2</v>
+      </c>
+      <c r="H42">
+        <v>-5.4039999999999999</v>
+      </c>
+      <c r="I42">
         <v>0</v>
       </c>
       <c r="J42" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>75</v>
       </c>
@@ -1970,29 +1992,29 @@
       <c r="C43" t="s">
         <v>84</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>-0.191</v>
       </c>
-      <c r="E43" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-0.043</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-7.773</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="E43">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F43">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+      <c r="G43">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="H43">
+        <v>-7.7729999999999997</v>
+      </c>
+      <c r="I43">
         <v>0</v>
       </c>
       <c r="J43" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -2002,29 +2024,29 @@
       <c r="C44" t="s">
         <v>85</v>
       </c>
-      <c r="D44" t="n">
-        <v>-1.047</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="D44">
+        <v>-1.0469999999999999</v>
+      </c>
+      <c r="E44">
         <v>0.114</v>
       </c>
-      <c r="F44" t="n">
-        <v>-0.583</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-3.708</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.0002</v>
+      <c r="F44">
+        <v>-0.58299999999999996</v>
+      </c>
+      <c r="G44">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="H44">
+        <v>-3.7080000000000002</v>
+      </c>
+      <c r="I44">
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="J44" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -2034,29 +2056,29 @@
       <c r="C45" t="s">
         <v>86</v>
       </c>
-      <c r="D45" t="n">
-        <v>-7.761</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="D45">
+        <v>-7.7610000000000001</v>
+      </c>
+      <c r="E45">
         <v>0.312</v>
       </c>
-      <c r="F45" t="n">
-        <v>-4.691</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="F45">
+        <v>-4.6909999999999998</v>
+      </c>
+      <c r="G45">
         <v>0.156</v>
       </c>
-      <c r="H45" t="n">
-        <v>-8.801</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="H45">
+        <v>-8.8010000000000002</v>
+      </c>
+      <c r="I45">
         <v>0</v>
       </c>
       <c r="J45" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>75</v>
       </c>
@@ -2066,29 +2088,29 @@
       <c r="C46" t="s">
         <v>76</v>
       </c>
-      <c r="D46" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1.209</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="D46">
+        <v>1.2230000000000001</v>
+      </c>
+      <c r="E46">
+        <v>6.3E-2</v>
+      </c>
+      <c r="F46">
+        <v>1.2090000000000001</v>
+      </c>
+      <c r="G46">
         <v>0.05</v>
       </c>
-      <c r="H46" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.866</v>
+      <c r="H46">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="I46">
+        <v>0.86599999999999999</v>
       </c>
       <c r="J46" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2098,29 +2120,29 @@
       <c r="C47" t="s">
         <v>78</v>
       </c>
-      <c r="D47" t="n">
-        <v>-1.807</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="G47" t="n">
+      <c r="D47">
+        <v>-1.8069999999999999</v>
+      </c>
+      <c r="E47">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="F47">
+        <v>-2.1800000000000002</v>
+      </c>
+      <c r="G47">
         <v>0.3</v>
       </c>
-      <c r="H47" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.3542</v>
+      <c r="H47">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="I47">
+        <v>0.35420000000000001</v>
       </c>
       <c r="J47" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -2130,29 +2152,29 @@
       <c r="C48" t="s">
         <v>80</v>
       </c>
-      <c r="D48" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H48" t="n">
+      <c r="D48">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="E48">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="F48">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="G48">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H48">
         <v>1.456</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>0.1454</v>
       </c>
       <c r="J48" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>75</v>
       </c>
@@ -2162,29 +2184,29 @@
       <c r="C49" t="s">
         <v>81</v>
       </c>
-      <c r="D49" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="E49" t="n">
+      <c r="D49">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="E49">
         <v>0.121</v>
       </c>
-      <c r="F49" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="H49" t="n">
-        <v>1.116</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.2644</v>
+      <c r="F49">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="G49">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H49">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="I49">
+        <v>0.26440000000000002</v>
       </c>
       <c r="J49" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -2194,29 +2216,29 @@
       <c r="C50" t="s">
         <v>83</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>-0.315</v>
       </c>
-      <c r="E50" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.384</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H50" t="n">
+      <c r="E50">
+        <v>2.7E-2</v>
+      </c>
+      <c r="F50">
+        <v>-0.38400000000000001</v>
+      </c>
+      <c r="G50">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H50">
         <v>1.86</v>
       </c>
-      <c r="I50" t="n">
-        <v>0.0629</v>
+      <c r="I50">
+        <v>6.2899999999999998E-2</v>
       </c>
       <c r="J50" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>75</v>
       </c>
@@ -2226,29 +2248,29 @@
       <c r="C51" t="s">
         <v>84</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>-0.191</v>
       </c>
-      <c r="E51" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F51" t="n">
+      <c r="E51">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F51">
         <v>-0.216</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H51" t="n">
+      <c r="G51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H51">
         <v>1.056</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>0.2908</v>
       </c>
       <c r="J51" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>75</v>
       </c>
@@ -2258,29 +2280,29 @@
       <c r="C52" t="s">
         <v>85</v>
       </c>
-      <c r="D52" t="n">
-        <v>-1.047</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="D52">
+        <v>-1.0469999999999999</v>
+      </c>
+      <c r="E52">
         <v>0.114</v>
       </c>
-      <c r="F52" t="n">
-        <v>-0.903</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="H52" t="n">
+      <c r="F52">
+        <v>-0.90300000000000002</v>
+      </c>
+      <c r="G52">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H52">
         <v>-1.012</v>
       </c>
-      <c r="I52" t="n">
-        <v>0.3117</v>
+      <c r="I52">
+        <v>0.31169999999999998</v>
       </c>
       <c r="J52" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -2290,29 +2312,29 @@
       <c r="C53" t="s">
         <v>86</v>
       </c>
-      <c r="D53" t="n">
-        <v>-7.761</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="D53">
+        <v>-7.7610000000000001</v>
+      </c>
+      <c r="E53">
         <v>0.312</v>
       </c>
-      <c r="F53" t="n">
-        <v>-8.449</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="F53">
+        <v>-8.4489999999999998</v>
+      </c>
+      <c r="G53">
         <v>0.245</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>1.736</v>
       </c>
-      <c r="I53" t="n">
-        <v>0.0826</v>
+      <c r="I53">
+        <v>8.2600000000000007E-2</v>
       </c>
       <c r="J53" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>87</v>
       </c>
@@ -2322,29 +2344,29 @@
       <c r="C54" t="s">
         <v>76</v>
       </c>
-      <c r="D54" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1.209</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="D54">
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="E54">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="F54">
+        <v>1.2090000000000001</v>
+      </c>
+      <c r="G54">
         <v>0.05</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>9.734</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>0</v>
       </c>
       <c r="J54" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>87</v>
       </c>
@@ -2354,29 +2376,29 @@
       <c r="C55" t="s">
         <v>78</v>
       </c>
-      <c r="D55" t="n">
-        <v>-2.046</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="D55">
+        <v>-2.0459999999999998</v>
+      </c>
+      <c r="E55">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="F55">
+        <v>-2.1800000000000002</v>
+      </c>
+      <c r="G55">
         <v>0.3</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>0.373</v>
       </c>
-      <c r="I55" t="n">
-        <v>0.7091</v>
+      <c r="I55">
+        <v>0.70909999999999995</v>
       </c>
       <c r="J55" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>87</v>
       </c>
@@ -2386,29 +2408,29 @@
       <c r="C56" t="s">
         <v>80</v>
       </c>
-      <c r="D56" t="n">
-        <v>-0.073</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="D56">
+        <v>-7.2999999999999995E-2</v>
+      </c>
+      <c r="E56">
         <v>0.05</v>
       </c>
-      <c r="F56" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-3.171</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.0015</v>
+      <c r="F56">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="G56">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H56">
+        <v>-3.1709999999999998</v>
+      </c>
+      <c r="I56">
+        <v>1.5E-3</v>
       </c>
       <c r="J56" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>87</v>
       </c>
@@ -2418,29 +2440,29 @@
       <c r="C57" t="s">
         <v>81</v>
       </c>
-      <c r="D57" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.586</v>
+      <c r="D57">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="E57">
+        <v>7.8E-2</v>
+      </c>
+      <c r="F57">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="G57">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H57">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="I57">
+        <v>0.58599999999999997</v>
       </c>
       <c r="J57" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -2450,29 +2472,29 @@
       <c r="C58" t="s">
         <v>83</v>
       </c>
-      <c r="D58" t="n">
-        <v>-0.148</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.384</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H58" t="n">
-        <v>8.276</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="D58">
+        <v>-0.14799999999999999</v>
+      </c>
+      <c r="E58">
+        <v>1.4E-2</v>
+      </c>
+      <c r="F58">
+        <v>-0.38400000000000001</v>
+      </c>
+      <c r="G58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H58">
+        <v>8.2759999999999998</v>
+      </c>
+      <c r="I58">
         <v>0</v>
       </c>
       <c r="J58" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -2482,29 +2504,29 @@
       <c r="C59" t="s">
         <v>84</v>
       </c>
-      <c r="D59" t="n">
-        <v>-0.043</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="F59" t="n">
+      <c r="D59">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+      <c r="E59">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F59">
         <v>-0.216</v>
       </c>
-      <c r="G59" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H59" t="n">
+      <c r="G59">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H59">
         <v>10.353</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>0</v>
       </c>
       <c r="J59" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>87</v>
       </c>
@@ -2514,29 +2536,29 @@
       <c r="C60" t="s">
         <v>85</v>
       </c>
-      <c r="D60" t="n">
-        <v>-0.583</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.903</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="H60" t="n">
-        <v>3.192</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.0014</v>
+      <c r="D60">
+        <v>-0.58299999999999996</v>
+      </c>
+      <c r="E60">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="F60">
+        <v>-0.90300000000000002</v>
+      </c>
+      <c r="G60">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H60">
+        <v>3.1920000000000002</v>
+      </c>
+      <c r="I60">
+        <v>1.4E-3</v>
       </c>
       <c r="J60" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -2546,22 +2568,22 @@
       <c r="C61" t="s">
         <v>86</v>
       </c>
-      <c r="D61" t="n">
-        <v>-4.691</v>
-      </c>
-      <c r="E61" t="n">
+      <c r="D61">
+        <v>-4.6909999999999998</v>
+      </c>
+      <c r="E61">
         <v>0.156</v>
       </c>
-      <c r="F61" t="n">
-        <v>-8.449</v>
-      </c>
-      <c r="G61" t="n">
+      <c r="F61">
+        <v>-8.4489999999999998</v>
+      </c>
+      <c r="G61">
         <v>0.245</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>12.95</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>0</v>
       </c>
       <c r="J61" t="s">
@@ -2570,39 +2592,39 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2625,7 +2647,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2648,7 +2670,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -2671,7 +2693,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2694,7 +2716,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -2717,7 +2739,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -2740,7 +2762,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -2763,7 +2785,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -2786,12 +2808,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -2823,7 +2845,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>145</v>
       </c>
@@ -2833,29 +2855,29 @@
       <c r="C14" t="s">
         <v>76</v>
       </c>
-      <c r="D14" t="n">
-        <v>1.499</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="D14">
+        <v>1.4990000000000001</v>
+      </c>
+      <c r="E14">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="F14">
         <v>1.93</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-3.501</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0005</v>
+      <c r="G14">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="H14">
+        <v>-3.5009999999999999</v>
+      </c>
+      <c r="I14">
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="J14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>145</v>
       </c>
@@ -2865,29 +2887,29 @@
       <c r="C15" t="s">
         <v>78</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>-0.47</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.151</v>
       </c>
-      <c r="F15" t="n">
-        <v>-2.466</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="H15" t="n">
-        <v>7.787</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="F15">
+        <v>-2.4660000000000002</v>
+      </c>
+      <c r="G15">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="H15">
+        <v>7.7869999999999999</v>
+      </c>
+      <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>145</v>
       </c>
@@ -2897,29 +2919,29 @@
       <c r="C16" t="s">
         <v>80</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.558</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.242</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="D16">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="E16">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="F16">
+        <v>-0.24199999999999999</v>
+      </c>
+      <c r="G16">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="H16">
         <v>7.84</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>145</v>
       </c>
@@ -2929,29 +2951,29 @@
       <c r="C17" t="s">
         <v>81</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="D17">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="E17">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F17">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G17">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="H17">
         <v>2.351</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.0187</v>
+      <c r="I17">
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="J17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>145</v>
       </c>
@@ -2961,29 +2983,29 @@
       <c r="C18" t="s">
         <v>83</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>-0.24</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.169</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.0114</v>
+      <c r="E18">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F18">
+        <v>-0.16900000000000001</v>
+      </c>
+      <c r="G18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H18">
+        <v>-2.5299999999999998</v>
+      </c>
+      <c r="I18">
+        <v>1.14E-2</v>
       </c>
       <c r="J18" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>145</v>
       </c>
@@ -2993,29 +3015,29 @@
       <c r="C19" t="s">
         <v>84</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>-0.09</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.068</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="H19" t="n">
+      <c r="E19">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F19">
+        <v>-6.8000000000000005E-2</v>
+      </c>
+      <c r="G19">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H19">
         <v>-1.446</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.1481</v>
+      <c r="I19">
+        <v>0.14810000000000001</v>
       </c>
       <c r="J19" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>145</v>
       </c>
@@ -3025,29 +3047,29 @@
       <c r="C20" t="s">
         <v>85</v>
       </c>
-      <c r="D20" t="n">
-        <v>-0.988</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.616</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-3.163</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.0016</v>
+      <c r="D20">
+        <v>-0.98799999999999999</v>
+      </c>
+      <c r="E20">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F20">
+        <v>-0.61599999999999999</v>
+      </c>
+      <c r="G20">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="H20">
+        <v>-3.1629999999999998</v>
+      </c>
+      <c r="I20">
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="J20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>145</v>
       </c>
@@ -3057,29 +3079,29 @@
       <c r="C21" t="s">
         <v>86</v>
       </c>
-      <c r="D21" t="n">
-        <v>-6.586</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21">
+        <v>-6.5860000000000003</v>
+      </c>
+      <c r="E21">
         <v>0.31</v>
       </c>
-      <c r="F21" t="n">
-        <v>-5.137</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="F21">
+        <v>-5.1369999999999996</v>
+      </c>
+      <c r="G21">
         <v>0.17</v>
       </c>
-      <c r="H21" t="n">
-        <v>-4.095</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H21">
+        <v>-4.0949999999999998</v>
+      </c>
+      <c r="I21">
         <v>0</v>
       </c>
       <c r="J21" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>145</v>
       </c>
@@ -3089,29 +3111,29 @@
       <c r="C22" t="s">
         <v>76</v>
       </c>
-      <c r="D22" t="n">
-        <v>1.499</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.164</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.183</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.0015</v>
+      <c r="D22">
+        <v>1.4990000000000001</v>
+      </c>
+      <c r="E22">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="F22">
+        <v>1.1639999999999999</v>
+      </c>
+      <c r="G22">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H22">
+        <v>3.1829999999999998</v>
+      </c>
+      <c r="I22">
+        <v>1.5E-3</v>
       </c>
       <c r="J22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>145</v>
       </c>
@@ -3121,29 +3143,29 @@
       <c r="C23" t="s">
         <v>78</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>-0.47</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.151</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>-1.038</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.735</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.0828</v>
+      <c r="G23">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H23">
+        <v>1.7350000000000001</v>
+      </c>
+      <c r="I23">
+        <v>8.2799999999999999E-2</v>
       </c>
       <c r="J23" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>145</v>
       </c>
@@ -3153,29 +3175,29 @@
       <c r="C24" t="s">
         <v>80</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.558</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="D24">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="E24">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="F24">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="G24">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="H24">
         <v>-0.246</v>
       </c>
-      <c r="I24" t="n">
-        <v>0.806</v>
+      <c r="I24">
+        <v>0.80600000000000005</v>
       </c>
       <c r="J24" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>145</v>
       </c>
@@ -3185,29 +3207,29 @@
       <c r="C25" t="s">
         <v>81</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.5374</v>
+      <c r="D25">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="E25">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F25">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="G25">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="H25">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="I25">
+        <v>0.53739999999999999</v>
       </c>
       <c r="J25" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>145</v>
       </c>
@@ -3217,29 +3239,29 @@
       <c r="C26" t="s">
         <v>83</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>-0.24</v>
       </c>
-      <c r="E26" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.352</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="E26">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F26">
+        <v>-0.35199999999999998</v>
+      </c>
+      <c r="G26">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H26">
         <v>2.83</v>
       </c>
-      <c r="I26" t="n">
-        <v>0.0047</v>
+      <c r="I26">
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="J26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>145</v>
       </c>
@@ -3249,29 +3271,29 @@
       <c r="C27" t="s">
         <v>84</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>-0.09</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0.196</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="E27">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F27">
+        <v>-0.19600000000000001</v>
+      </c>
+      <c r="G27">
+        <v>1.9E-2</v>
+      </c>
+      <c r="H27">
         <v>4.625</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>0</v>
       </c>
       <c r="J27" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>145</v>
       </c>
@@ -3281,29 +3303,29 @@
       <c r="C28" t="s">
         <v>85</v>
       </c>
-      <c r="D28" t="n">
-        <v>-0.988</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-1.033</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.7707</v>
+      <c r="D28">
+        <v>-0.98799999999999999</v>
+      </c>
+      <c r="E28">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F28">
+        <v>-1.0329999999999999</v>
+      </c>
+      <c r="G28">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="H28">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="I28">
+        <v>0.77070000000000005</v>
       </c>
       <c r="J28" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>145</v>
       </c>
@@ -3313,29 +3335,29 @@
       <c r="C29" t="s">
         <v>86</v>
       </c>
-      <c r="D29" t="n">
-        <v>-6.586</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29">
+        <v>-6.5860000000000003</v>
+      </c>
+      <c r="E29">
         <v>0.31</v>
       </c>
-      <c r="F29" t="n">
-        <v>-8.521</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="F29">
+        <v>-8.5210000000000008</v>
+      </c>
+      <c r="G29">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="H29">
         <v>3.907</v>
       </c>
-      <c r="I29" t="n">
-        <v>0.0001</v>
+      <c r="I29">
+        <v>1E-4</v>
       </c>
       <c r="J29" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>145</v>
       </c>
@@ -3345,29 +3367,29 @@
       <c r="C30" t="s">
         <v>76</v>
       </c>
-      <c r="D30" t="n">
-        <v>1.499</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.071</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-0.119</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.9049</v>
+      <c r="D30">
+        <v>1.4990000000000001</v>
+      </c>
+      <c r="E30">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="F30">
+        <v>1.5109999999999999</v>
+      </c>
+      <c r="G30">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="H30">
+        <v>-0.11899999999999999</v>
+      </c>
+      <c r="I30">
+        <v>0.90490000000000004</v>
       </c>
       <c r="J30" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>145</v>
       </c>
@@ -3377,29 +3399,29 @@
       <c r="C31" t="s">
         <v>78</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>-0.47</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>0.151</v>
       </c>
-      <c r="F31" t="n">
-        <v>-3.756</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="H31" t="n">
-        <v>7.537</v>
-      </c>
-      <c r="I31" t="n">
+      <c r="F31">
+        <v>-3.7559999999999998</v>
+      </c>
+      <c r="G31">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="H31">
+        <v>7.5369999999999999</v>
+      </c>
+      <c r="I31">
         <v>0</v>
       </c>
       <c r="J31" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>145</v>
       </c>
@@ -3409,29 +3431,29 @@
       <c r="C32" t="s">
         <v>80</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.558</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-0.325</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H32" t="n">
-        <v>7.878</v>
-      </c>
-      <c r="I32" t="n">
+      <c r="D32">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="E32">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="F32">
+        <v>-0.32500000000000001</v>
+      </c>
+      <c r="G32">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H32">
+        <v>7.8780000000000001</v>
+      </c>
+      <c r="I32">
         <v>0</v>
       </c>
       <c r="J32" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>145</v>
       </c>
@@ -3441,29 +3463,29 @@
       <c r="C33" t="s">
         <v>81</v>
       </c>
-      <c r="D33" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.429</v>
+      <c r="D33">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="E33">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F33">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="G33">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="H33">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="I33">
+        <v>0.42899999999999999</v>
       </c>
       <c r="J33" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>145</v>
       </c>
@@ -3473,29 +3495,29 @@
       <c r="C34" t="s">
         <v>83</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>-0.24</v>
       </c>
-      <c r="E34" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.288</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="E34">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F34">
+        <v>-0.28799999999999998</v>
+      </c>
+      <c r="G34">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="H34">
         <v>1.516</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>0.1295</v>
       </c>
       <c r="J34" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>145</v>
       </c>
@@ -3505,29 +3527,29 @@
       <c r="C35" t="s">
         <v>84</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>-0.09</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E35">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F35">
         <v>-0.13</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.253</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.0243</v>
+      <c r="G35">
+        <v>1.2E-2</v>
+      </c>
+      <c r="H35">
+        <v>2.2530000000000001</v>
+      </c>
+      <c r="I35">
+        <v>2.4299999999999999E-2</v>
       </c>
       <c r="J35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>145</v>
       </c>
@@ -3537,29 +3559,29 @@
       <c r="C36" t="s">
         <v>85</v>
       </c>
-      <c r="D36" t="n">
-        <v>-0.988</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="F36" t="n">
+      <c r="D36">
+        <v>-0.98799999999999999</v>
+      </c>
+      <c r="E36">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F36">
         <v>-0.81</v>
       </c>
-      <c r="G36" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="G36">
+        <v>7.8E-2</v>
+      </c>
+      <c r="H36">
         <v>-1.42</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>0.1555</v>
       </c>
       <c r="J36" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>145</v>
       </c>
@@ -3569,29 +3591,29 @@
       <c r="C37" t="s">
         <v>86</v>
       </c>
-      <c r="D37" t="n">
-        <v>-6.586</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="D37">
+        <v>-6.5860000000000003</v>
+      </c>
+      <c r="E37">
         <v>0.31</v>
       </c>
-      <c r="F37" t="n">
-        <v>-7.208</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F37">
+        <v>-7.2080000000000002</v>
+      </c>
+      <c r="G37">
         <v>0.22</v>
       </c>
-      <c r="H37" t="n">
-        <v>1.636</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="H37">
+        <v>1.6359999999999999</v>
+      </c>
+      <c r="I37">
         <v>0.1018</v>
       </c>
       <c r="J37" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>146</v>
       </c>
@@ -3601,29 +3623,29 @@
       <c r="C38" t="s">
         <v>76</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>1.93</v>
       </c>
-      <c r="E38" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.164</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="H38" t="n">
-        <v>6.674</v>
-      </c>
-      <c r="I38" t="n">
+      <c r="E38">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="F38">
+        <v>1.1639999999999999</v>
+      </c>
+      <c r="G38">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H38">
+        <v>6.6740000000000004</v>
+      </c>
+      <c r="I38">
         <v>0</v>
       </c>
       <c r="J38" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>146</v>
       </c>
@@ -3633,29 +3655,29 @@
       <c r="C39" t="s">
         <v>78</v>
       </c>
-      <c r="D39" t="n">
-        <v>-2.466</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="D39">
+        <v>-2.4660000000000002</v>
+      </c>
+      <c r="E39">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="F39">
         <v>-1.038</v>
       </c>
-      <c r="G39" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-4.001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.0001</v>
+      <c r="G39">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H39">
+        <v>-4.0010000000000003</v>
+      </c>
+      <c r="I39">
+        <v>1E-4</v>
       </c>
       <c r="J39" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>146</v>
       </c>
@@ -3665,29 +3687,29 @@
       <c r="C40" t="s">
         <v>80</v>
       </c>
-      <c r="D40" t="n">
-        <v>-0.242</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-7.137</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="D40">
+        <v>-0.24199999999999999</v>
+      </c>
+      <c r="E40">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="F40">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="G40">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="H40">
+        <v>-7.1369999999999996</v>
+      </c>
+      <c r="I40">
         <v>0</v>
       </c>
       <c r="J40" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>146</v>
       </c>
@@ -3697,29 +3719,29 @@
       <c r="C41" t="s">
         <v>81</v>
       </c>
-      <c r="D41" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-1.697</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.0897</v>
+      <c r="D41">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="E41">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F41">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="G41">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="H41">
+        <v>-1.6970000000000001</v>
+      </c>
+      <c r="I41">
+        <v>8.9700000000000002E-2</v>
       </c>
       <c r="J41" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>146</v>
       </c>
@@ -3729,29 +3751,29 @@
       <c r="C42" t="s">
         <v>83</v>
       </c>
-      <c r="D42" t="n">
-        <v>-0.169</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-0.352</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="D42">
+        <v>-0.16900000000000001</v>
+      </c>
+      <c r="E42">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F42">
+        <v>-0.35199999999999998</v>
+      </c>
+      <c r="G42">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H42">
         <v>5.141</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>0</v>
       </c>
       <c r="J42" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>146</v>
       </c>
@@ -3761,29 +3783,29 @@
       <c r="C43" t="s">
         <v>84</v>
       </c>
-      <c r="D43" t="n">
-        <v>-0.068</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-0.196</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="H43" t="n">
-        <v>6.065</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="D43">
+        <v>-6.8000000000000005E-2</v>
+      </c>
+      <c r="E43">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="F43">
+        <v>-0.19600000000000001</v>
+      </c>
+      <c r="G43">
+        <v>1.9E-2</v>
+      </c>
+      <c r="H43">
+        <v>6.0650000000000004</v>
+      </c>
+      <c r="I43">
         <v>0</v>
       </c>
       <c r="J43" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>146</v>
       </c>
@@ -3793,29 +3815,29 @@
       <c r="C44" t="s">
         <v>85</v>
       </c>
-      <c r="D44" t="n">
-        <v>-0.616</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-1.033</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3.072</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.0021</v>
+      <c r="D44">
+        <v>-0.61599999999999999</v>
+      </c>
+      <c r="E44">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F44">
+        <v>-1.0329999999999999</v>
+      </c>
+      <c r="G44">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="H44">
+        <v>3.0720000000000001</v>
+      </c>
+      <c r="I44">
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="J44" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -3825,29 +3847,29 @@
       <c r="C45" t="s">
         <v>86</v>
       </c>
-      <c r="D45" t="n">
-        <v>-5.137</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="D45">
+        <v>-5.1369999999999996</v>
+      </c>
+      <c r="E45">
         <v>0.17</v>
       </c>
-      <c r="F45" t="n">
-        <v>-8.521</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="H45" t="n">
-        <v>8.018</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="F45">
+        <v>-8.5210000000000008</v>
+      </c>
+      <c r="G45">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="H45">
+        <v>8.0180000000000007</v>
+      </c>
+      <c r="I45">
         <v>0</v>
       </c>
       <c r="J45" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>146</v>
       </c>
@@ -3857,29 +3879,29 @@
       <c r="C46" t="s">
         <v>76</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>1.93</v>
       </c>
-      <c r="E46" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.071</v>
-      </c>
-      <c r="H46" t="n">
+      <c r="E46">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="F46">
+        <v>1.5109999999999999</v>
+      </c>
+      <c r="G46">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="H46">
         <v>3.577</v>
       </c>
-      <c r="I46" t="n">
-        <v>0.0003</v>
+      <c r="I46">
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="J46" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>146</v>
       </c>
@@ -3889,29 +3911,29 @@
       <c r="C47" t="s">
         <v>78</v>
       </c>
-      <c r="D47" t="n">
-        <v>-2.466</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-3.756</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="H47" t="n">
-        <v>2.813</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.0049</v>
+      <c r="D47">
+        <v>-2.4660000000000002</v>
+      </c>
+      <c r="E47">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="F47">
+        <v>-3.7559999999999998</v>
+      </c>
+      <c r="G47">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="H47">
+        <v>2.8130000000000002</v>
+      </c>
+      <c r="I47">
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="J47" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>146</v>
       </c>
@@ -3921,29 +3943,29 @@
       <c r="C48" t="s">
         <v>80</v>
       </c>
-      <c r="D48" t="n">
-        <v>-0.242</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-0.325</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.4247</v>
+      <c r="D48">
+        <v>-0.24199999999999999</v>
+      </c>
+      <c r="E48">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="F48">
+        <v>-0.32500000000000001</v>
+      </c>
+      <c r="G48">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H48">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="I48">
+        <v>0.42470000000000002</v>
       </c>
       <c r="J48" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>146</v>
       </c>
@@ -3953,29 +3975,29 @@
       <c r="C49" t="s">
         <v>81</v>
       </c>
-      <c r="D49" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-1.078</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.2812</v>
+      <c r="D49">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="E49">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F49">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="G49">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="H49">
+        <v>-1.0780000000000001</v>
+      </c>
+      <c r="I49">
+        <v>0.28120000000000001</v>
       </c>
       <c r="J49" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>146</v>
       </c>
@@ -3985,29 +4007,29 @@
       <c r="C50" t="s">
         <v>83</v>
       </c>
-      <c r="D50" t="n">
-        <v>-0.169</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.288</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="H50" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="I50" t="n">
+      <c r="D50">
+        <v>-0.16900000000000001</v>
+      </c>
+      <c r="E50">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F50">
+        <v>-0.28799999999999998</v>
+      </c>
+      <c r="G50">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="H50">
+        <v>4.4669999999999996</v>
+      </c>
+      <c r="I50">
         <v>0</v>
       </c>
       <c r="J50" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -4017,29 +4039,29 @@
       <c r="C51" t="s">
         <v>84</v>
       </c>
-      <c r="D51" t="n">
-        <v>-0.068</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="F51" t="n">
+      <c r="D51">
+        <v>-6.8000000000000005E-2</v>
+      </c>
+      <c r="E51">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="F51">
         <v>-0.13</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="H51" t="n">
-        <v>4.049</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.0001</v>
+      <c r="G51">
+        <v>1.2E-2</v>
+      </c>
+      <c r="H51">
+        <v>4.0490000000000004</v>
+      </c>
+      <c r="I51">
+        <v>1E-4</v>
       </c>
       <c r="J51" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>146</v>
       </c>
@@ -4049,29 +4071,29 @@
       <c r="C52" t="s">
         <v>85</v>
       </c>
-      <c r="D52" t="n">
-        <v>-0.616</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F52" t="n">
+      <c r="D52">
+        <v>-0.61599999999999999</v>
+      </c>
+      <c r="E52">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F52">
         <v>-0.81</v>
       </c>
-      <c r="G52" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1.914</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.0556</v>
+      <c r="G52">
+        <v>7.8E-2</v>
+      </c>
+      <c r="H52">
+        <v>1.9139999999999999</v>
+      </c>
+      <c r="I52">
+        <v>5.5599999999999997E-2</v>
       </c>
       <c r="J52" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>146</v>
       </c>
@@ -4081,29 +4103,29 @@
       <c r="C53" t="s">
         <v>86</v>
       </c>
-      <c r="D53" t="n">
-        <v>-5.137</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="D53">
+        <v>-5.1369999999999996</v>
+      </c>
+      <c r="E53">
         <v>0.17</v>
       </c>
-      <c r="F53" t="n">
-        <v>-7.208</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="F53">
+        <v>-7.2080000000000002</v>
+      </c>
+      <c r="G53">
         <v>0.22</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>7.444</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53">
         <v>0</v>
       </c>
       <c r="J53" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>147</v>
       </c>
@@ -4113,29 +4135,29 @@
       <c r="C54" t="s">
         <v>76</v>
       </c>
-      <c r="D54" t="n">
-        <v>1.164</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.071</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-3.553</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.0004</v>
+      <c r="D54">
+        <v>1.1639999999999999</v>
+      </c>
+      <c r="E54">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="F54">
+        <v>1.5109999999999999</v>
+      </c>
+      <c r="G54">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="H54">
+        <v>-3.5529999999999999</v>
+      </c>
+      <c r="I54">
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="J54" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>147</v>
       </c>
@@ -4145,29 +4167,29 @@
       <c r="C55" t="s">
         <v>78</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>-1.038</v>
       </c>
-      <c r="E55" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-3.756</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="H55" t="n">
-        <v>5.418</v>
-      </c>
-      <c r="I55" t="n">
+      <c r="E55">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="F55">
+        <v>-3.7559999999999998</v>
+      </c>
+      <c r="G55">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="H55">
+        <v>5.4180000000000001</v>
+      </c>
+      <c r="I55">
         <v>0</v>
       </c>
       <c r="J55" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>147</v>
       </c>
@@ -4177,29 +4199,29 @@
       <c r="C56" t="s">
         <v>80</v>
       </c>
-      <c r="D56" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.325</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H56" t="n">
-        <v>7.293</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="D56">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="E56">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="F56">
+        <v>-0.32500000000000001</v>
+      </c>
+      <c r="G56">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H56">
+        <v>7.2930000000000001</v>
+      </c>
+      <c r="I56">
         <v>0</v>
       </c>
       <c r="J56" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>147</v>
       </c>
@@ -4209,29 +4231,29 @@
       <c r="C57" t="s">
         <v>81</v>
       </c>
-      <c r="D57" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="H57" t="n">
+      <c r="D57">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="E57">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F57">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="G57">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="H57">
         <v>0.313</v>
       </c>
-      <c r="I57" t="n">
-        <v>0.7543</v>
+      <c r="I57">
+        <v>0.75429999999999997</v>
       </c>
       <c r="J57" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>147</v>
       </c>
@@ -4241,29 +4263,29 @@
       <c r="C58" t="s">
         <v>83</v>
       </c>
-      <c r="D58" t="n">
-        <v>-0.352</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.288</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-1.648</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.0993</v>
+      <c r="D58">
+        <v>-0.35199999999999998</v>
+      </c>
+      <c r="E58">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F58">
+        <v>-0.28799999999999998</v>
+      </c>
+      <c r="G58">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="H58">
+        <v>-1.6479999999999999</v>
+      </c>
+      <c r="I58">
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="J58" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>147</v>
       </c>
@@ -4273,29 +4295,29 @@
       <c r="C59" t="s">
         <v>84</v>
       </c>
-      <c r="D59" t="n">
-        <v>-0.196</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F59" t="n">
+      <c r="D59">
+        <v>-0.19600000000000001</v>
+      </c>
+      <c r="E59">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F59">
         <v>-0.13</v>
       </c>
-      <c r="G59" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-2.889</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.0039</v>
+      <c r="G59">
+        <v>1.2E-2</v>
+      </c>
+      <c r="H59">
+        <v>-2.8889999999999998</v>
+      </c>
+      <c r="I59">
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="J59" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -4305,29 +4327,29 @@
       <c r="C60" t="s">
         <v>85</v>
       </c>
-      <c r="D60" t="n">
-        <v>-1.033</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="F60" t="n">
+      <c r="D60">
+        <v>-1.0329999999999999</v>
+      </c>
+      <c r="E60">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F60">
         <v>-0.81</v>
       </c>
-      <c r="G60" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-1.565</v>
-      </c>
-      <c r="I60" t="n">
+      <c r="G60">
+        <v>7.8E-2</v>
+      </c>
+      <c r="H60">
+        <v>-1.5649999999999999</v>
+      </c>
+      <c r="I60">
         <v>0.1176</v>
       </c>
       <c r="J60" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>147</v>
       </c>
@@ -4337,23 +4359,23 @@
       <c r="C61" t="s">
         <v>86</v>
       </c>
-      <c r="D61" t="n">
-        <v>-8.521</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-7.208</v>
-      </c>
-      <c r="G61" t="n">
+      <c r="D61">
+        <v>-8.5210000000000008</v>
+      </c>
+      <c r="E61">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="F61">
+        <v>-7.2080000000000002</v>
+      </c>
+      <c r="G61">
         <v>0.22</v>
       </c>
-      <c r="H61" t="n">
-        <v>-2.953</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.0031</v>
+      <c r="H61">
+        <v>-2.9529999999999998</v>
+      </c>
+      <c r="I61">
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="J61" t="s">
         <v>79</v>
@@ -4361,6 +4383,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>